--- a/rules/CORE-000354/negative/01/data/unit-test-coreid-CG0007-negative-01.xlsx
+++ b/rules/CORE-000354/negative/01/data/unit-test-coreid-CG0007-negative-01.xlsx
@@ -1919,9 +1919,7 @@
       <c r="S5" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="T5" s="4" t="s">
-        <v>20</v>
-      </c>
+      <c r="T5" s="4"/>
       <c r="U5" s="4">
         <v>1</v>
       </c>
@@ -1984,9 +1982,7 @@
       <c r="S6" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="T6" s="4" t="s">
-        <v>20</v>
-      </c>
+      <c r="T6" s="4"/>
       <c r="U6" s="4">
         <v>141</v>
       </c>
